--- a/performance_tracking_forms/003_recording_quality_assessment--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/003_recording_quality_assessment--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'distorted'}</t>
+          <t>distorted</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Distorted'}</t>
+          <t>Distorted</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'hard_to_understand'}</t>
+          <t>hard_to_understand</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Hard to Understand'}</t>
+          <t>Hard to Understand</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Fast'}</t>
+          <t>Fast</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Slow'}</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'mp3'}</t>
+          <t>mp3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'MP3'}</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'wav'}</t>
+          <t>wav</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'WAV'}</t>
+          <t>WAV</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'mp4'}</t>
+          <t>mp4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'MP4'}</t>
+          <t>MP4</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'wav'}</t>
+          <t>wav</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Wav'}</t>
+          <t>Wav</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
